--- a/Doc/Validation_FMKIO.xlsx
+++ b/Doc/Validation_FMKIO.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Software\STM32\f_designHRTIM\src\1_FMK\FMK_HAL\FMK_IO\Doc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Software\STM32\Gamma_fMotionPlanner\src\1_FMK\FMK_HAL\FMK_IO\Doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B17EE93F-B38A-4E22-BB18-5908393DCEE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFDF857B-0A83-41C3-B267-9AD4B571B492}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B654A100-FC4B-4AD6-8CD5-7BE8F9D1ACE1}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B654A100-FC4B-4AD6-8CD5-7BE8F9D1ACE1}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="102">
   <si>
     <t>Signal Name</t>
   </si>
@@ -321,6 +321,27 @@
   </si>
   <si>
     <t>9d115988</t>
+  </si>
+  <si>
+    <t>PA9</t>
+  </si>
+  <si>
+    <t>Freq  Change</t>
+  </si>
+  <si>
+    <t>DC Change</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pulse </t>
+  </si>
+  <si>
+    <t>PWM6-7</t>
+  </si>
+  <si>
+    <t>PA9 et PC2</t>
+  </si>
+  <si>
+    <t>Pulse Sync</t>
   </si>
 </sst>
 </file>
@@ -389,8 +410,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D85C0DC8-4B53-4406-A1A5-399EBE39C1B4}" name="Tableau1" displayName="Tableau1" ref="D19:K61" totalsRowShown="0">
-  <autoFilter ref="D19:K61" xr:uid="{D85C0DC8-4B53-4406-A1A5-399EBE39C1B4}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D85C0DC8-4B53-4406-A1A5-399EBE39C1B4}" name="Tableau1" displayName="Tableau1" ref="D19:K65" totalsRowShown="0">
+  <autoFilter ref="D19:K65" xr:uid="{D85C0DC8-4B53-4406-A1A5-399EBE39C1B4}"/>
   <tableColumns count="8">
     <tableColumn id="7" xr3:uid="{85E5D1C5-8EBA-4AC8-8A4B-D875ED539E63}" name="Signal Name"/>
     <tableColumn id="1" xr3:uid="{E9808153-524F-4B4B-B49A-8E4CBC854CC4}" name="Bsp Name"/>
@@ -733,7 +754,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{634BA75F-9645-4262-9D67-E06FEFBAB9A9}">
-  <dimension ref="B3:K61"/>
+  <dimension ref="B3:K65"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="27" customWidth="1"/>
@@ -1667,6 +1688,74 @@
         <v>94</v>
       </c>
     </row>
+    <row r="62" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D62" t="s">
+        <v>42</v>
+      </c>
+      <c r="E62" t="s">
+        <v>95</v>
+      </c>
+      <c r="F62" t="s">
+        <v>41</v>
+      </c>
+      <c r="G62" t="s">
+        <v>96</v>
+      </c>
+      <c r="H62" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="63" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D63" t="s">
+        <v>42</v>
+      </c>
+      <c r="E63" t="s">
+        <v>95</v>
+      </c>
+      <c r="F63" t="s">
+        <v>41</v>
+      </c>
+      <c r="G63" t="s">
+        <v>97</v>
+      </c>
+      <c r="H63" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="64" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D64" t="s">
+        <v>42</v>
+      </c>
+      <c r="E64" t="s">
+        <v>95</v>
+      </c>
+      <c r="F64" t="s">
+        <v>41</v>
+      </c>
+      <c r="G64" t="s">
+        <v>98</v>
+      </c>
+      <c r="H64" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="65" spans="4:8" x14ac:dyDescent="0.3">
+      <c r="D65" t="s">
+        <v>99</v>
+      </c>
+      <c r="E65" t="s">
+        <v>100</v>
+      </c>
+      <c r="F65" t="s">
+        <v>41</v>
+      </c>
+      <c r="G65" t="s">
+        <v>101</v>
+      </c>
+      <c r="H65" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
